--- a/data/infraestructura-core/meridian-toll-road.xlsx
+++ b/data/infraestructura-core/meridian-toll-road.xlsx
@@ -19,6 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InsightsLenders" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CreditMetrics" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CashFlowWaterfall" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -605,6 +607,18 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>transactionRole</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -953,6 +967,207 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>#</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DSCR Min.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.14×</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DSCR Avg.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.23×</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LLCR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.35×</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PLCR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.48×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Concession Tail</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CADS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>68</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Senior Debt Service</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>52</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DSRA Funding</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MRA / MMRA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Distributable Dividend</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>end</t>
         </is>
       </c>
     </row>
